--- a/kraje.xlsx
+++ b/kraje.xlsx
@@ -454,28 +454,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cook Islands</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cook Islands</t>
+          <t>Republic of Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ck.png</t>
+          <t>https://flagcdn.com/w320/ci.png</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15040</v>
+        <v>31719275</v>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -485,28 +485,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Republic of Guinea</t>
+          <t>Italian Republic</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gn.png</t>
+          <t>https://flagcdn.com/w320/it.png</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14363931</v>
+        <v>58927633</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
     </row>
@@ -516,28 +516,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Christmas Island</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Territory of Christmas Island</t>
+          <t>Kyrgyz Republic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cx.png</t>
+          <t>https://flagcdn.com/w320/kg.png</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1692</v>
+        <v>7281800</v>
       </c>
       <c r="F4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>Central Asia</t>
         </is>
       </c>
     </row>
@@ -547,28 +547,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Togolese Republic</t>
+          <t>Independent State of Papua New Guinea</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tg.png</t>
+          <t>https://flagcdn.com/w320/pg.png</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8095498</v>
+        <v>11781559</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Melanesia</t>
         </is>
       </c>
     </row>
@@ -578,28 +578,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Fiji</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of China (Taiwan)</t>
+          <t>Republic of Fiji</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tw.png</t>
+          <t>https://flagcdn.com/w320/fj.png</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23317031</v>
+        <v>900869</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Melanesia</t>
         </is>
       </c>
     </row>
@@ -609,28 +609,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kyrgyz Republic</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/kg.png</t>
+          <t>https://flagcdn.com/w320/ae.png</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7281800</v>
+        <v>11294243</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -640,28 +640,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Saint Kitts and Nevis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Suriname</t>
+          <t>Federation of Saint Christopher and Nevis</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sr.png</t>
+          <t>https://flagcdn.com/w320/kn.png</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>616500</v>
+        <v>51320</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -671,28 +671,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>French Guiana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guiana</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/do.png</t>
+          <t>https://flagcdn.com/w320/gf.png</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10771504</v>
+        <v>292354</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -702,28 +702,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Guatemala</t>
+          <t>United Republic of Tanzania</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gt.png</t>
+          <t>https://flagcdn.com/w320/tz.png</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18079810</v>
+        <v>68153004</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -733,28 +733,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>People's Democratic Republic of Algeria</t>
+          <t>Republic of Angola</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/dz.png</t>
+          <t>https://flagcdn.com/w320/ao.png</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47400000</v>
+        <v>36170961</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
     </row>
@@ -764,28 +764,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Togolese Republic</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ua.png</t>
+          <t>https://flagcdn.com/w320/tg.png</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>32862000</v>
+        <v>8095498</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -795,28 +795,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Saint Kitts and Nevis</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Federation of Saint Christopher and Nevis</t>
+          <t>Republic of Finland</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/kn.png</t>
+          <t>https://flagcdn.com/w320/fi.png</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>51320</v>
+        <v>5650325</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -826,28 +826,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Croatia</t>
+          <t>Republic of Malawi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/hr.png</t>
+          <t>https://flagcdn.com/w320/mw.png</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3866233</v>
+        <v>20734262</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Southeast Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -857,28 +857,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Equatorial Guinea</t>
+          <t>Republic of Mali</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gq.png</t>
+          <t>https://flagcdn.com/w320/ml.png</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1668768</v>
+        <v>22395489</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -888,28 +888,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Panama</t>
+          <t>Republic of Uzbekistan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pa.png</t>
+          <t>https://flagcdn.com/w320/uz.png</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4064780</v>
+        <v>37859698</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Central Asia</t>
         </is>
       </c>
     </row>
@@ -919,28 +919,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kingdom of Belgium</t>
+          <t>Republic of Senegal</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/be.png</t>
+          <t>https://flagcdn.com/w320/sn.png</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11825551</v>
+        <v>18593258</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -950,26 +950,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bouvet Island</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bouvet Island</t>
+          <t>Republic of Uganda</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bv.png</t>
+          <t>https://flagcdn.com/w320/ug.png</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>45905417</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Eastern Africa</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -977,21 +981,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Rwanda</t>
+          <t>Republic of Djibouti</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/rw.png</t>
+          <t>https://flagcdn.com/w320/dj.png</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14104969</v>
+        <v>1066809</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -1008,26 +1012,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>French Southern and Antarctic Lands</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Territory of the French Southern and Antarctic Lands</t>
+          <t>Republic of South Sudan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tf.png</t>
+          <t>https://flagcdn.com/w320/ss.png</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>400</v>
+        <v>15786898</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Middle Africa</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1035,28 +1043,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Jersey</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Cabo Verde</t>
+          <t>Bailiwick of Jersey</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cv.png</t>
+          <t>https://flagcdn.com/w320/je.png</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>491233</v>
+        <v>103267</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -1066,28 +1074,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Korea</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/kr.png</t>
+          <t>https://flagcdn.com/w320/tv.png</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>51159889</v>
+        <v>10643</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Polynesia</t>
         </is>
       </c>
     </row>
@@ -1097,28 +1105,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gu.png</t>
+          <t>https://flagcdn.com/w320/jp.png</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>153836</v>
+        <v>123210000</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -1128,28 +1136,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Principality of Andorra</t>
+          <t>Sultanate of Oman</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ad.png</t>
+          <t>https://flagcdn.com/w320/om.png</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>88406</v>
+        <v>5343630</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -1159,28 +1167,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Senegal</t>
+          <t>Kingdom of Belgium</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sn.png</t>
+          <t>https://flagcdn.com/w320/be.png</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>18593258</v>
+        <v>11825551</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Western Europe</t>
         </is>
       </c>
     </row>
@@ -1190,28 +1198,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Saint Martin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oriental Republic of Uruguay</t>
+          <t>Saint Martin</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/uy.png</t>
+          <t>https://flagcdn.com/w320/mf.png</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3499451</v>
+        <v>31496</v>
       </c>
       <c r="F26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -1221,28 +1229,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Republic of the Congo</t>
+          <t>Mayotte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of the Congo</t>
+          <t>Department of Mayotte</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cg.png</t>
+          <t>https://flagcdn.com/w320/yt.png</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6142180</v>
+        <v>320901</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -1252,28 +1260,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Namibia</t>
+          <t>French Republic</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/na.png</t>
+          <t>https://flagcdn.com/w320/fr.png</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3022401</v>
+        <v>66351959</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Western Europe</t>
         </is>
       </c>
     </row>
@@ -1283,28 +1291,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Singapore</t>
+          <t>Republic of Bulgaria</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sg.png</t>
+          <t>https://flagcdn.com/w320/bg.png</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6110200</v>
+        <v>6437360</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>South-Eastern Asia</t>
+          <t>Southeast Europe</t>
         </is>
       </c>
     </row>
@@ -1314,28 +1322,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Finland</t>
+          <t>Republic of Cyprus</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/fi.png</t>
+          <t>https://flagcdn.com/w320/cy.png</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5650325</v>
+        <v>1442614</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
     </row>
@@ -1345,28 +1353,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arab Republic of Egypt</t>
+          <t>Republic of Korea</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/eg.png</t>
+          <t>https://flagcdn.com/w320/kr.png</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>107271260</v>
+        <v>51159889</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -1376,28 +1384,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Palau</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Palau</t>
+          <t>United Mexican States</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pw.png</t>
+          <t>https://flagcdn.com/w320/mx.png</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>16733</v>
+        <v>130575786</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -1407,28 +1415,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Samoa</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>American Samoa</t>
+          <t>Republic of North Macedonia</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/as.png</t>
+          <t>https://flagcdn.com/w320/mk.png</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>49710</v>
+        <v>1822612</v>
       </c>
       <c r="F33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Southeast Europe</t>
         </is>
       </c>
     </row>
@@ -1438,28 +1446,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Antigua and Barbuda</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Antigua and Barbuda</t>
+          <t>Co-operative Republic of Guyana</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ag.png</t>
+          <t>https://flagcdn.com/w320/gy.png</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103603</v>
+        <v>772975</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -1469,28 +1477,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Kosovo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Seychelles</t>
+          <t>Republic of Kosovo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sc.png</t>
+          <t>https://flagcdn.com/w320/xk.png</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>122729</v>
+        <v>1585566</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southeast Europe</t>
         </is>
       </c>
     </row>
@@ -1500,28 +1508,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>State of Kuwait</t>
+          <t>Kingdom of Morocco</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/kw.png</t>
+          <t>https://flagcdn.com/w320/ma.png</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4881254</v>
+        <v>36828330</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Northern Africa</t>
         </is>
       </c>
     </row>
@@ -1531,24 +1539,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Gibraltar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hellenic Republic</t>
+          <t>Gibraltar</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gr.png</t>
+          <t>https://flagcdn.com/w320/gi.png</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10400720</v>
+        <v>38000</v>
       </c>
       <c r="F37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1562,28 +1570,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kiribati</t>
+          <t>Western Sahara</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Independent and Sovereign Republic of Kiribati</t>
+          <t>Sahrawi Arab Democratic Republic</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ki.png</t>
+          <t>https://flagcdn.com/w320/eh.png</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>120740</v>
+        <v>600904</v>
       </c>
       <c r="F38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Northern Africa</t>
         </is>
       </c>
     </row>
@@ -1593,21 +1601,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Cyprus</t>
+          <t>Principality of Andorra</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cy.png</t>
+          <t>https://flagcdn.com/w320/ad.png</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1442614</v>
+        <v>88406</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -1624,28 +1632,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Palau</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Mali</t>
+          <t>Republic of Palau</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ml.png</t>
+          <t>https://flagcdn.com/w320/pw.png</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>22395489</v>
+        <v>16733</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Micronesia</t>
         </is>
       </c>
     </row>
@@ -1655,28 +1663,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bermuda</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bermuda</t>
+          <t>Republic of Guinea</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bm.png</t>
+          <t>https://flagcdn.com/w320/gn.png</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>64055</v>
+        <v>14363931</v>
       </c>
       <c r="F41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -1686,28 +1694,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Turks and Caicos Islands</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Turks and Caicos Islands</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gl.png</t>
+          <t>https://flagcdn.com/w320/tc.png</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>56542</v>
+        <v>50828</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -1717,28 +1725,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>State of Eritrea</t>
+          <t>Kingdom of Saudi Arabia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/er.png</t>
+          <t>https://flagcdn.com/w320/sa.png</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3607000</v>
+        <v>35300280</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -1748,28 +1756,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>United Republic of Tanzania</t>
+          <t>Republic of Botswana</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tz.png</t>
+          <t>https://flagcdn.com/w320/bw.png</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>68153004</v>
+        <v>2359609</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
     </row>
@@ -1779,28 +1787,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Socialist Republic of Vietnam</t>
+          <t>Union of the Comoros</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/vn.png</t>
+          <t>https://flagcdn.com/w320/km.png</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101343800</v>
+        <v>919901</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>South-Eastern Asia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -1810,28 +1818,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Chad</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/td.png</t>
+          <t>https://flagcdn.com/w320/bz.png</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>19340757</v>
+        <v>417634</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Central America</t>
         </is>
       </c>
     </row>
@@ -1841,28 +1849,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Côte d'Ivoire</t>
+          <t>Kingdom of Cambodia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ci.png</t>
+          <t>https://flagcdn.com/w320/kh.png</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>31719275</v>
+        <v>17577760</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -1872,28 +1880,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Saint Lucia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Saint Lucia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ge.png</t>
+          <t>https://flagcdn.com/w320/lc.png</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4000921</v>
+        <v>184100</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -1903,28 +1911,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Isle of Man</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Isle of Man</t>
+          <t>Islamic Republic of Mauritania</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/im.png</t>
+          <t>https://flagcdn.com/w320/mr.png</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>84530</v>
+        <v>4927532</v>
       </c>
       <c r="F49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -1934,26 +1942,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>South Georgia</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Georgia and the South Sandwich Islands</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gs.png</t>
+          <t>https://flagcdn.com/w320/jm.png</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>2825544</v>
       </c>
       <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1961,28 +1973,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plurinational State of Bolivia</t>
+          <t>Republic of Cabo Verde</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bo.png</t>
+          <t>https://flagcdn.com/w320/cv.png</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11365333</v>
+        <v>491233</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -1992,28 +2004,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>United States Minor Outlying Islands</t>
+          <t>Marshall Islands</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>United States Minor Outlying Islands</t>
+          <t>Republic of the Marshall Islands</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/um.png</t>
+          <t>https://flagcdn.com/w320/mh.png</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>42418</v>
       </c>
       <c r="F52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Micronesia</t>
         </is>
       </c>
     </row>
@@ -2023,28 +2035,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kingdom of Denmark</t>
+          <t>Republic of Namibia</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/dk.png</t>
+          <t>https://flagcdn.com/w320/na.png</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6011488</v>
+        <v>3022401</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Southern Africa</t>
         </is>
       </c>
     </row>
@@ -2054,28 +2066,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Islamic Republic of Iran</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tm.png</t>
+          <t>https://flagcdn.com/w320/ir.png</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7057841</v>
+        <v>85961000</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Southern Asia</t>
         </is>
       </c>
     </row>
@@ -2085,28 +2097,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Wallis and Futuna</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Republic of Niger</t>
+          <t>Territory of the Wallis and Futuna Islands</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ne.png</t>
+          <t>https://flagcdn.com/w320/wf.png</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>26312034</v>
+        <v>11620</v>
       </c>
       <c r="F55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Polynesia</t>
         </is>
       </c>
     </row>
@@ -2116,28 +2128,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Federated States of Micronesia</t>
+          <t>Republic of Azerbaijan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/fm.png</t>
+          <t>https://flagcdn.com/w320/az.png</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105564</v>
+        <v>10241722</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -2147,28 +2159,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jersey</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bailiwick of Jersey</t>
+          <t>Republic of Niger</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/je.png</t>
+          <t>https://flagcdn.com/w320/ne.png</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103267</v>
+        <v>26312034</v>
       </c>
       <c r="F57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -2178,30 +2190,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cayman Islands</t>
+          <t>Heard Island and McDonald Islands</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cayman Islands</t>
+          <t>Heard Island and McDonald Islands</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ky.png</t>
+          <t>https://flagcdn.com/w320/hm.png</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>84738</v>
+        <v>0</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2209,28 +2217,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Liechtenstein</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Principality of Liechtenstein</t>
+          <t>Lao People's Democratic Republic</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/li.png</t>
+          <t>https://flagcdn.com/w320/la.png</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>40900</v>
+        <v>7647000</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -2240,28 +2248,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ba.png</t>
+          <t>https://flagcdn.com/w320/bf.png</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3422000</v>
+        <v>24070553</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Southeast Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -2271,28 +2279,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Cocos (Keeling) Islands</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>French Republic</t>
+          <t>Territory of the Cocos (Keeling) Islands</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/fr.png</t>
+          <t>https://flagcdn.com/w320/cc.png</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>66351959</v>
+        <v>593</v>
       </c>
       <c r="F61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
     </row>
@@ -2302,28 +2310,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>French Polynesia</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>French Polynesia</t>
+          <t>Grand Duchy of Luxembourg</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pf.png</t>
+          <t>https://flagcdn.com/w320/lu.png</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>279500</v>
+        <v>681973</v>
       </c>
       <c r="F62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Western Europe</t>
         </is>
       </c>
     </row>
@@ -2333,28 +2341,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Republic of Kazakhstan</t>
+          <t>Republic of Indonesia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/kz.png</t>
+          <t>https://flagcdn.com/w320/id.png</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>20426568</v>
+        <v>284438782</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -2364,28 +2372,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Republic of Angola</t>
+          <t>Lebanese Republic</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ao.png</t>
+          <t>https://flagcdn.com/w320/lb.png</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>36170961</v>
+        <v>5490000</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -2395,28 +2403,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Republic of Turkey</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/nz.png</t>
+          <t>https://flagcdn.com/w320/tr.png</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5324700</v>
+        <v>85664944</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -2426,28 +2434,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Commonwealth of Puerto Rico</t>
+          <t>Democratic Republic of Timor-Leste</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pr.png</t>
+          <t>https://flagcdn.com/w320/tl.png</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3203295</v>
+        <v>1391221</v>
       </c>
       <c r="F66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -2457,28 +2465,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kingdom of Saudi Arabia</t>
+          <t>Republic of Zimbabwe</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sa.png</t>
+          <t>https://flagcdn.com/w320/zw.png</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>35300280</v>
+        <v>17073087</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Africa</t>
         </is>
       </c>
     </row>
@@ -2488,28 +2496,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Republic of South Africa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/me.png</t>
+          <t>https://flagcdn.com/w320/za.png</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>623327</v>
+        <v>63100945</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Southeast Europe</t>
+          <t>Southern Africa</t>
         </is>
       </c>
     </row>
@@ -2519,28 +2527,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of South Africa</t>
+          <t>Republic of Armenia</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/za.png</t>
+          <t>https://flagcdn.com/w320/am.png</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>63100945</v>
+        <v>3076200</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -2550,28 +2558,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Islamic Republic of Pakistan</t>
+          <t>Republic of Ireland</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pk.png</t>
+          <t>https://flagcdn.com/w320/ie.png</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>241499431</v>
+        <v>5458600</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -2581,28 +2589,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Democratic Socialist Republic of Sri Lanka</t>
+          <t>Kingdom of Norway</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/lk.png</t>
+          <t>https://flagcdn.com/w320/no.png</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>21763170</v>
+        <v>5606944</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -2612,28 +2620,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Cameroon</t>
+          <t>Republic of Kenya</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cm.png</t>
+          <t>https://flagcdn.com/w320/ke.png</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>29442327</v>
+        <v>53330978</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -2643,28 +2651,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Guernsey</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bailiwick of Guernsey</t>
+          <t>Democratic People's Republic of Korea</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gg.png</t>
+          <t>https://flagcdn.com/w320/kp.png</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>64781</v>
+        <v>25950000</v>
       </c>
       <c r="F73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -2674,28 +2682,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Liberia</t>
+          <t>Islamic Republic of Afghanistan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/lr.png</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Flag_of_the_Taliban.svg/320px-Flag_of_the_Taliban.svg.png</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5248621</v>
+        <v>43844000</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Southern Asia</t>
         </is>
       </c>
     </row>
@@ -2705,28 +2713,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Bermuda</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Bermuda</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ae.png</t>
+          <t>https://flagcdn.com/w320/bm.png</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>11294243</v>
+        <v>64055</v>
       </c>
       <c r="F75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -2736,28 +2744,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Swiss Confederation</t>
+          <t>Kingdom of Spain</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ch.png</t>
+          <t>https://flagcdn.com/w320/es.png</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>9082848</v>
+        <v>49315949</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
     </row>
@@ -2767,28 +2775,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Kingdom of the Netherlands</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/hu.png</t>
+          <t>https://flagcdn.com/w320/nl.png</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>9539502</v>
+        <v>18100436</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>Western Europe</t>
         </is>
       </c>
     </row>
@@ -2798,28 +2806,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>State of Libya</t>
+          <t>Republic of Nicaragua</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ly.png</t>
+          <t>https://flagcdn.com/w320/ni.png</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>7459000</v>
+        <v>6803886</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Central America</t>
         </is>
       </c>
     </row>
@@ -2829,28 +2837,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Vanuatu</t>
+          <t>Kingdom of Lesotho</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/vu.png</t>
+          <t>https://flagcdn.com/w320/ls.png</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>321409</v>
+        <v>2116427</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Southern Africa</t>
         </is>
       </c>
     </row>
@@ -2860,28 +2868,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wallis and Futuna</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Territory of the Wallis and Futuna Islands</t>
+          <t>Arab Republic of Egypt</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/wf.png</t>
+          <t>https://flagcdn.com/w320/eg.png</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>11620</v>
+        <v>107271260</v>
       </c>
       <c r="F80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Northern Africa</t>
         </is>
       </c>
     </row>
@@ -2891,28 +2899,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Saint Lucia</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saint Lucia</t>
+          <t>Republic of the Gambia</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/lc.png</t>
+          <t>https://flagcdn.com/w320/gm.png</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>184100</v>
+        <v>2422712</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -2922,28 +2930,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Federative Republic of Brazil</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cf.png</t>
+          <t>https://flagcdn.com/w320/br.png</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6470307</v>
+        <v>213421037</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -2953,28 +2961,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Tajikistan</t>
+          <t>Commonwealth of Australia</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tj.png</t>
+          <t>https://flagcdn.com/w320/au.png</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>10499000</v>
+        <v>27536874</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
     </row>
@@ -2984,30 +2992,26 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Bouvet Island</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland</t>
+          <t>Bouvet Island</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ie.png</t>
+          <t>https://flagcdn.com/w320/bv.png</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5458600</v>
+        <v>0</v>
       </c>
       <c r="F84" t="b">
-        <v>1</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3015,28 +3019,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>New Caledonia</t>
+          <t>Pitcairn Islands</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New Caledonia</t>
+          <t>Pitcairn Group of Islands</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/nc.png</t>
+          <t>https://flagcdn.com/w320/pn.png</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>264596</v>
+        <v>35</v>
       </c>
       <c r="F85" t="b">
         <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Polynesia</t>
         </is>
       </c>
     </row>
@@ -3046,28 +3050,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Yemen</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ye.png</t>
+          <t>https://flagcdn.com/w320/bb.png</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>32684503</v>
+        <v>267800</v>
       </c>
       <c r="F86" t="b">
         <v>1</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -3077,28 +3081,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Faroe Islands</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Faroe Islands</t>
+          <t>Republic of Madagascar</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/fo.png</t>
+          <t>https://flagcdn.com/w320/mg.png</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>54885</v>
+        <v>31727042</v>
       </c>
       <c r="F87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -3108,28 +3112,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Cuba</t>
+          <t>United Kingdom of Great Britain and Northern Ireland</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cu.png</t>
+          <t>https://flagcdn.com/w320/gb.png</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>9748007</v>
+        <v>69281437</v>
       </c>
       <c r="F88" t="b">
         <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -3139,28 +3143,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Azerbaijan</t>
+          <t>Portuguese Republic</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/az.png</t>
+          <t>https://flagcdn.com/w320/pt.png</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>10241722</v>
+        <v>10749635</v>
       </c>
       <c r="F89" t="b">
         <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Europe</t>
         </is>
       </c>
     </row>
@@ -3170,28 +3174,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sb.png</t>
+          <t>https://flagcdn.com/w320/gl.png</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>750325</v>
+        <v>56542</v>
       </c>
       <c r="F90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -3201,28 +3205,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>American Samoa</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>American Samoa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/jm.png</t>
+          <t>https://flagcdn.com/w320/as.png</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2825544</v>
+        <v>49710</v>
       </c>
       <c r="F91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Polynesia</t>
         </is>
       </c>
     </row>
@@ -3232,30 +3236,26 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Georgia</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kingdom of Morocco</t>
+          <t>South Georgia and the South Sandwich Islands</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ma.png</t>
+          <t>https://flagcdn.com/w320/gs.png</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>36828330</v>
+        <v>0</v>
       </c>
       <c r="F92" t="b">
-        <v>1</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Northern Africa</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3263,28 +3263,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Trinidad and Tobago</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tt.png</t>
+          <t>https://flagcdn.com/w320/tm.png</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1367764</v>
+        <v>7057841</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Central Asia</t>
         </is>
       </c>
     </row>
@@ -3294,28 +3294,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mayotte</t>
+          <t>Guadeloupe</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Department of Mayotte</t>
+          <t>Guadeloupe</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/yt.png</t>
+          <t>https://flagcdn.com/w320/gp.png</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>320901</v>
+        <v>378561</v>
       </c>
       <c r="F94" t="b">
         <v>0</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -3325,28 +3325,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Niue</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Niue</t>
+          <t>Commonwealth of Dominica</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/nu.png</t>
+          <t>https://flagcdn.com/w320/dm.png</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1681</v>
+        <v>67408</v>
       </c>
       <c r="F95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -3356,28 +3356,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Solomon Islands</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Solomon Islands</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bz.png</t>
+          <t>https://flagcdn.com/w320/sb.png</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>417634</v>
+        <v>750325</v>
       </c>
       <c r="F96" t="b">
         <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Melanesia</t>
         </is>
       </c>
     </row>
@@ -3387,28 +3387,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Saint Pierre and Miquelon</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>People's Republic of China</t>
+          <t>Saint Pierre and Miquelon</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cn.png</t>
+          <t>https://flagcdn.com/w320/pm.png</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1408280000</v>
+        <v>5819</v>
       </c>
       <c r="F97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -3418,28 +3418,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Independent State of Samoa</t>
+          <t>Republic of Rwanda</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ws.png</t>
+          <t>https://flagcdn.com/w320/rw.png</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>205557</v>
+        <v>14104969</v>
       </c>
       <c r="F98" t="b">
         <v>1</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -3449,28 +3449,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>British Virgin Islands</t>
+          <t>Norfolk Island</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Virgin Islands</t>
+          <t>Territory of Norfolk Island</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/vg.png</t>
+          <t>https://flagcdn.com/w320/nf.png</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>39471</v>
+        <v>2188</v>
       </c>
       <c r="F99" t="b">
         <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
     </row>
@@ -3480,28 +3480,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of the Sudan</t>
+          <t>Republic of Panama</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sd.png</t>
+          <t>https://flagcdn.com/w320/pa.png</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>51662000</v>
+        <v>4064780</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Central America</t>
         </is>
       </c>
     </row>
@@ -3511,28 +3511,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Norfolk Island</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Territory of Norfolk Island</t>
+          <t>Commonwealth of the Bahamas</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/nf.png</t>
+          <t>https://flagcdn.com/w320/bs.png</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2188</v>
+        <v>398165</v>
       </c>
       <c r="F101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -3542,28 +3542,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Tokelau</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Slovak Republic</t>
+          <t>Tokelau</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sk.png</t>
+          <t>https://flagcdn.com/w320/tk.png</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5413813</v>
+        <v>2608</v>
       </c>
       <c r="F102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>Polynesia</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3573,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Burundi</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bi.png</t>
+          <t>https://flagcdn.com/w320/me.png</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>12332788</v>
+        <v>623327</v>
       </c>
       <c r="F103" t="b">
         <v>1</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southeast Europe</t>
         </is>
       </c>
     </row>
@@ -3604,28 +3604,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Marshall Islands</t>
+          <t>Åland Islands</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of the Marshall Islands</t>
+          <t>Åland Islands</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mh.png</t>
+          <t>https://flagcdn.com/w320/ax.png</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>42418</v>
+        <v>30654</v>
       </c>
       <c r="F104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -3635,28 +3635,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Niue</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Austria</t>
+          <t>Niue</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/at.png</t>
+          <t>https://flagcdn.com/w320/nu.png</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>9200931</v>
+        <v>1681</v>
       </c>
       <c r="F105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>Polynesia</t>
         </is>
       </c>
     </row>
@@ -3666,28 +3666,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Mozambique</t>
+          <t>Argentine Republic</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mz.png</t>
+          <t>https://flagcdn.com/w320/ar.png</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>34090466</v>
+        <v>46735004</v>
       </c>
       <c r="F106" t="b">
         <v>1</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -3697,21 +3697,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Saint Vincent and the Grenadines</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Saint Vincent and the Grenadines</t>
+          <t>Republic of Cuba</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/vc.png</t>
+          <t>https://flagcdn.com/w320/cu.png</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>110872</v>
+        <v>9748007</v>
       </c>
       <c r="F107" t="b">
         <v>1</v>
@@ -3728,28 +3728,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Cayman Islands</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Independent State of Papua New Guinea</t>
+          <t>Cayman Islands</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pg.png</t>
+          <t>https://flagcdn.com/w320/ky.png</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>11781559</v>
+        <v>84738</v>
       </c>
       <c r="F108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -3759,28 +3759,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Turkey</t>
+          <t>Republic of Kazakhstan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tr.png</t>
+          <t>https://flagcdn.com/w320/kz.png</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>85664944</v>
+        <v>20426568</v>
       </c>
       <c r="F109" t="b">
         <v>1</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Central Asia</t>
         </is>
       </c>
     </row>
@@ -3790,28 +3790,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Kosovo</t>
+          <t>Russian Federation</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/xk.png</t>
+          <t>https://flagcdn.com/w320/ru.png</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1585566</v>
+        <v>146028325</v>
       </c>
       <c r="F110" t="b">
         <v>1</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Southeast Europe</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
     </row>
@@ -3821,28 +3821,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Republic of India</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gd.png</t>
+          <t>https://flagcdn.com/w320/in.png</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>109021</v>
+        <v>1417492000</v>
       </c>
       <c r="F111" t="b">
         <v>1</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Southern Asia</t>
         </is>
       </c>
     </row>
@@ -3852,28 +3852,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>British Virgin Islands</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kingdom of Cambodia</t>
+          <t>Virgin Islands</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/kh.png</t>
+          <t>https://flagcdn.com/w320/vg.png</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>17577760</v>
+        <v>39471</v>
       </c>
       <c r="F112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>South-Eastern Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -3883,28 +3883,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portuguese Republic</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pt.png</t>
+          <t>https://flagcdn.com/w320/gu.png</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>10749635</v>
+        <v>153836</v>
       </c>
       <c r="F113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Micronesia</t>
         </is>
       </c>
     </row>
@@ -3914,28 +3914,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>United Kingdom of Great Britain and Northern Ireland</t>
+          <t>Republic of the Union of Myanmar</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gb.png</t>
+          <t>https://flagcdn.com/w320/mm.png</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>69281437</v>
+        <v>51316756</v>
       </c>
       <c r="F114" t="b">
         <v>1</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -3945,28 +3945,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Federal Republic of Nigeria</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ng.png</t>
+          <t>https://flagcdn.com/w320/cd.png</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>223800000</v>
+        <v>112832000</v>
       </c>
       <c r="F115" t="b">
         <v>1</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
     </row>
@@ -3976,28 +3976,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Anguilla</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Anguilla</t>
+          <t>Republic of Mauritius</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ai.png</t>
+          <t>https://flagcdn.com/w320/mu.png</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>16010</v>
+        <v>1243741</v>
       </c>
       <c r="F116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -4007,28 +4007,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Northern Mariana Islands</t>
+          <t>Falkland Islands</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Commonwealth of the Northern Mariana Islands</t>
+          <t>Falkland Islands</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mp.png</t>
+          <t>https://flagcdn.com/w320/fk.png</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>47329</v>
+        <v>3662</v>
       </c>
       <c r="F117" t="b">
         <v>0</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -4038,28 +4038,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Northern Mariana Islands</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>State of Israel</t>
+          <t>Commonwealth of the Northern Mariana Islands</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/il.png</t>
+          <t>https://flagcdn.com/w320/mp.png</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>10134800</v>
+        <v>47329</v>
       </c>
       <c r="F118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Micronesia</t>
         </is>
       </c>
     </row>
@@ -4069,28 +4069,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>French Guiana</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Guiana</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gf.png</t>
+          <t>https://flagcdn.com/w320/ua.png</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>292354</v>
+        <v>32862000</v>
       </c>
       <c r="F119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
     </row>
@@ -4100,28 +4100,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lebanese Republic</t>
+          <t>Principality of Monaco</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/lb.png</t>
+          <t>https://flagcdn.com/w320/mc.png</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5490000</v>
+        <v>38423</v>
       </c>
       <c r="F120" t="b">
         <v>1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Western Europe</t>
         </is>
       </c>
     </row>
@@ -4131,28 +4131,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Republic of Tajikistan</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/jp.png</t>
+          <t>https://flagcdn.com/w320/tj.png</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>123210000</v>
+        <v>10499000</v>
       </c>
       <c r="F121" t="b">
         <v>1</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Central Asia</t>
         </is>
       </c>
     </row>
@@ -4162,28 +4162,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of the Gambia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gm.png</t>
+          <t>https://flagcdn.com/w320/my.png</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2422712</v>
+        <v>34231700</v>
       </c>
       <c r="F122" t="b">
         <v>1</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -4193,28 +4193,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Saint Martin</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saint Martin</t>
+          <t>Federal Republic of Somalia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mf.png</t>
+          <t>https://flagcdn.com/w320/so.png</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>31496</v>
+        <v>19655000</v>
       </c>
       <c r="F123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -4224,28 +4224,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Antigua and Barbuda</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Guinea-Bissau</t>
+          <t>Antigua and Barbuda</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gw.png</t>
+          <t>https://flagcdn.com/w320/ag.png</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1781308</v>
+        <v>103603</v>
       </c>
       <c r="F124" t="b">
         <v>1</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -4255,28 +4255,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lao People's Democratic Republic</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/la.png</t>
+          <t>https://flagcdn.com/w320/cf.png</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>7647000</v>
+        <v>6470307</v>
       </c>
       <c r="F125" t="b">
         <v>1</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>South-Eastern Asia</t>
+          <t>Middle Africa</t>
         </is>
       </c>
     </row>
@@ -4286,28 +4286,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of North Macedonia</t>
+          <t>Macao Special Administrative Region of the People's Republic of China</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mk.png</t>
+          <t>https://flagcdn.com/w320/mo.png</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1822612</v>
+        <v>685900</v>
       </c>
       <c r="F126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Southeast Europe</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -4317,21 +4317,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>State of Qatar</t>
+          <t>State of Israel</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/qa.png</t>
+          <t>https://flagcdn.com/w320/il.png</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3173024</v>
+        <v>10134800</v>
       </c>
       <c r="F127" t="b">
         <v>1</v>
@@ -4348,28 +4348,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Zambia</t>
+          <t>Federal Republic of Nigeria</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/zm.png</t>
+          <t>https://flagcdn.com/w320/ng.png</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>19693423</v>
+        <v>223800000</v>
       </c>
       <c r="F128" t="b">
         <v>1</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -4379,28 +4379,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Republic of Honduras</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bb.png</t>
+          <t>https://flagcdn.com/w320/hn.png</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>267800</v>
+        <v>9892632</v>
       </c>
       <c r="F129" t="b">
         <v>1</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Central America</t>
         </is>
       </c>
     </row>
@@ -4410,28 +4410,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Vatican City State</t>
+          <t>Republic of Sierra Leone</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/va.png</t>
+          <t>https://flagcdn.com/w320/sl.png</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>882</v>
+        <v>9077691</v>
       </c>
       <c r="F130" t="b">
         <v>1</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -4441,28 +4441,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italian Republic</t>
+          <t>Tunisian Republic</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/it.png</t>
+          <t>https://flagcdn.com/w320/tn.png</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>58927633</v>
+        <v>11972169</v>
       </c>
       <c r="F131" t="b">
         <v>1</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Northern Africa</t>
         </is>
       </c>
     </row>
@@ -4472,28 +4472,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Union of the Comoros</t>
+          <t>Republic of Lithuania</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/km.png</t>
+          <t>https://flagcdn.com/w320/lt.png</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>919901</v>
+        <v>2894886</v>
       </c>
       <c r="F132" t="b">
         <v>1</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -4503,28 +4503,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Republic of Albania</t>
+          <t>Republic of Iraq</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/al.png</t>
+          <t>https://flagcdn.com/w320/iq.png</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2363314</v>
+        <v>46118793</v>
       </c>
       <c r="F133" t="b">
         <v>1</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Southeast Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -4534,28 +4534,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Gibraltar</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Gibraltar</t>
+          <t>Swiss Confederation</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gi.png</t>
+          <t>https://flagcdn.com/w320/ch.png</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>38000</v>
+        <v>9082848</v>
       </c>
       <c r="F134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Western Europe</t>
         </is>
       </c>
     </row>
@@ -4565,28 +4565,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Republic of Chile</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mn.png</t>
+          <t>https://flagcdn.com/w320/cl.png</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3544835</v>
+        <v>20206953</v>
       </c>
       <c r="F135" t="b">
         <v>1</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -4596,28 +4596,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tonga</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kingdom of Tonga</t>
+          <t>Republic of China (Taiwan)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/to.png</t>
+          <t>https://flagcdn.com/w320/tw.png</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100179</v>
+        <v>23317031</v>
       </c>
       <c r="F136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -4627,28 +4627,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Republic of Madagascar</t>
+          <t>Socialist Republic of Vietnam</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mg.png</t>
+          <t>https://flagcdn.com/w320/vn.png</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>31727042</v>
+        <v>101343800</v>
       </c>
       <c r="F137" t="b">
         <v>1</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -4658,28 +4658,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Saint Pierre and Miquelon</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Saint Pierre and Miquelon</t>
+          <t>People's Republic of Bangladesh</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pm.png</t>
+          <t>https://flagcdn.com/w320/bd.png</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5819</v>
+        <v>169828911</v>
       </c>
       <c r="F138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Southern Asia</t>
         </is>
       </c>
     </row>
@@ -4689,28 +4689,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Saint Helena, Ascension and Tristan da Cunha</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Saint Helena, Ascension and Tristan da Cunha</t>
+          <t>Republic of Vanuatu</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sh.png</t>
+          <t>https://flagcdn.com/w320/vu.png</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5651</v>
+        <v>321409</v>
       </c>
       <c r="F139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Melanesia</t>
         </is>
       </c>
     </row>
@@ -4720,28 +4720,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Principality of Monaco</t>
+          <t>Islamic Republic of Pakistan</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mc.png</t>
+          <t>https://flagcdn.com/w320/pk.png</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>38423</v>
+        <v>241499431</v>
       </c>
       <c r="F140" t="b">
         <v>1</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Southern Asia</t>
         </is>
       </c>
     </row>
@@ -4751,28 +4751,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Federative Republic of Brazil</t>
+          <t>Republic of Latvia</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/br.png</t>
+          <t>https://flagcdn.com/w320/lv.png</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>213421037</v>
+        <v>1829000</v>
       </c>
       <c r="F141" t="b">
         <v>1</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -4782,28 +4782,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Commonwealth of Australia</t>
+          <t>Republic of Malta</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/au.png</t>
+          <t>https://flagcdn.com/w320/mt.png</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>27536874</v>
+        <v>574250</v>
       </c>
       <c r="F142" t="b">
         <v>1</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>Southern Europe</t>
         </is>
       </c>
     </row>
@@ -4813,28 +4813,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Co-operative Republic of Guyana</t>
+          <t>Republic of Seychelles</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gy.png</t>
+          <t>https://flagcdn.com/w320/sc.png</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>772975</v>
+        <v>122729</v>
       </c>
       <c r="F143" t="b">
         <v>1</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -4844,28 +4844,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Montserrat</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Republic of Slovenia</t>
+          <t>Montserrat</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/si.png</t>
+          <t>https://flagcdn.com/w320/ms.png</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2130638</v>
+        <v>4386</v>
       </c>
       <c r="F144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -4875,28 +4875,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Anguilla</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Republic of San Marino</t>
+          <t>Anguilla</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sm.png</t>
+          <t>https://flagcdn.com/w320/ai.png</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>34132</v>
+        <v>16010</v>
       </c>
       <c r="F145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -4906,28 +4906,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Tokelau</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tokelau</t>
+          <t>Hellenic Republic</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tk.png</t>
+          <t>https://flagcdn.com/w320/gr.png</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2608</v>
+        <v>10400720</v>
       </c>
       <c r="F146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Southern Europe</t>
         </is>
       </c>
     </row>
@@ -4937,28 +4937,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Palestine</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>State of Palestine</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ps.png</t>
+          <t>https://flagcdn.com/w320/cz.png</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5483450</v>
+        <v>10882341</v>
       </c>
       <c r="F147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Central Europe</t>
         </is>
       </c>
     </row>
@@ -4968,28 +4968,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Kingdom of Bhutan</t>
+          <t>Republic of Zambia</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bt.png</t>
+          <t>https://flagcdn.com/w320/zm.png</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>784043</v>
+        <v>19693423</v>
       </c>
       <c r="F148" t="b">
         <v>1</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -4999,28 +4999,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Sint Maarten</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sint Maarten</t>
+          <t>Hong Kong Special Administrative Region of the People's Republic of China</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sx.png</t>
+          <t>https://flagcdn.com/w320/hk.png</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>41349</v>
+        <v>7527500</v>
       </c>
       <c r="F149" t="b">
         <v>0</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -5030,28 +5030,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Republic of the Philippines</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ph.png</t>
+          <t>https://flagcdn.com/w320/us.png</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>114123600</v>
+        <v>340110988</v>
       </c>
       <c r="F150" t="b">
         <v>1</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>South-Eastern Asia</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -5061,28 +5061,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Republic of Chile</t>
+          <t>Kingdom of Eswatini</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cl.png</t>
+          <t>https://flagcdn.com/w320/sz.png</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>20206953</v>
+        <v>1235549</v>
       </c>
       <c r="F151" t="b">
         <v>1</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Southern Africa</t>
         </is>
       </c>
     </row>
@@ -5092,28 +5092,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Martinique</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Martinique</t>
+          <t>Republic of Slovenia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mq.png</t>
+          <t>https://flagcdn.com/w320/si.png</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>349925</v>
+        <v>2130638</v>
       </c>
       <c r="F152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Central Europe</t>
         </is>
       </c>
     </row>
@@ -5123,24 +5123,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Caribbean Netherlands</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Republic of Haiti</t>
+          <t>Bonaire, Sint Eustatius and Saba</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ht.png</t>
+          <t>https://flagcdn.com/w320/bq.png</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>11867032</v>
+        <v>31980</v>
       </c>
       <c r="F153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -5154,26 +5154,30 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Heard Island and McDonald Islands</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Heard Island and McDonald Islands</t>
+          <t>Republic of the Maldives</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/hm.png</t>
+          <t>https://flagcdn.com/w320/mv.png</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>515132</v>
       </c>
       <c r="F154" t="b">
-        <v>0</v>
-      </c>
-      <c r="G154" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Southern Asia</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5181,26 +5185,30 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Republic of Ghana</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/aq.png</t>
+          <t>https://flagcdn.com/w320/gh.png</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1300</v>
+        <v>33742380</v>
       </c>
       <c r="F155" t="b">
-        <v>0</v>
-      </c>
-      <c r="G155" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Western Africa</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5208,28 +5216,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>São Tomé and Príncipe</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Democratic Republic of São Tomé and Príncipe</t>
+          <t>Republic of Paraguay</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/st.png</t>
+          <t>https://flagcdn.com/w320/py.png</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>209607</v>
+        <v>6109644</v>
       </c>
       <c r="F156" t="b">
         <v>1</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -5239,28 +5247,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Macao Special Administrative Region of the People's Republic of China</t>
+          <t>Republic of Mozambique</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mo.png</t>
+          <t>https://flagcdn.com/w320/mz.png</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>685900</v>
+        <v>34090466</v>
       </c>
       <c r="F157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -5270,28 +5278,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Republic of Mauritius</t>
+          <t>State of Palestine</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mu.png</t>
+          <t>https://flagcdn.com/w320/ps.png</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1243741</v>
+        <v>5483450</v>
       </c>
       <c r="F158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -5301,28 +5309,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Kingdom of Bahrain</t>
+          <t>Republic of Moldova</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bh.png</t>
+          <t>https://flagcdn.com/w320/md.png</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1594654</v>
+        <v>2749076</v>
       </c>
       <c r="F159" t="b">
         <v>1</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
     </row>
@@ -5332,28 +5340,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>United Mexican States</t>
+          <t>Republic of Liberia</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mx.png</t>
+          <t>https://flagcdn.com/w320/lr.png</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>130575786</v>
+        <v>5248621</v>
       </c>
       <c r="F160" t="b">
         <v>1</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -5363,28 +5371,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Pitcairn Islands</t>
+          <t>Liechtenstein</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Pitcairn Group of Islands</t>
+          <t>Principality of Liechtenstein</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pn.png</t>
+          <t>https://flagcdn.com/w320/li.png</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>35</v>
+        <v>40900</v>
       </c>
       <c r="F161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Western Europe</t>
         </is>
       </c>
     </row>
@@ -5394,21 +5402,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Argentine Republic</t>
+          <t>Republic of Peru</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ar.png</t>
+          <t>https://flagcdn.com/w320/pe.png</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>46735004</v>
+        <v>34350244</v>
       </c>
       <c r="F162" t="b">
         <v>1</v>
@@ -5425,28 +5433,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Federal Democratic Republic of Nepal</t>
+          <t>State of Qatar</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/np.png</t>
+          <t>https://flagcdn.com/w320/qa.png</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>29911840</v>
+        <v>3173024</v>
       </c>
       <c r="F163" t="b">
         <v>1</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -5456,28 +5464,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Christmas Island</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kingdom of Sweden</t>
+          <t>Territory of Christmas Island</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/se.png</t>
+          <t>https://flagcdn.com/w320/cx.png</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>10605098</v>
+        <v>1692</v>
       </c>
       <c r="F164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
     </row>
@@ -5487,28 +5495,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Republic of Sierra Leone</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sl.png</t>
+          <t>https://flagcdn.com/w320/ge.png</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>9077691</v>
+        <v>4000921</v>
       </c>
       <c r="F165" t="b">
         <v>1</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -5518,28 +5526,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Kingdom of Eswatini</t>
+          <t>Republic of Ecuador</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sz.png</t>
+          <t>https://flagcdn.com/w320/ec.png</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1235549</v>
+        <v>18103660</v>
       </c>
       <c r="F166" t="b">
         <v>1</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -5549,28 +5557,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Kingdom of Spain</t>
+          <t>Republic of the Philippines</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/es.png</t>
+          <t>https://flagcdn.com/w320/ph.png</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>49315949</v>
+        <v>114123600</v>
       </c>
       <c r="F167" t="b">
         <v>1</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -5580,28 +5588,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Republic of Colombia</t>
+          <t>Federal Democratic Republic of Ethiopia</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/co.png</t>
+          <t>https://flagcdn.com/w320/et.png</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>53057212</v>
+        <v>111652998</v>
       </c>
       <c r="F168" t="b">
         <v>1</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -5611,21 +5619,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Turks and Caicos Islands</t>
+          <t>United States Virgin Islands</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Turks and Caicos Islands</t>
+          <t>Virgin Islands of the United States</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tc.png</t>
+          <t>https://flagcdn.com/w320/vi.png</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>50828</v>
+        <v>87146</v>
       </c>
       <c r="F169" t="b">
         <v>0</v>
@@ -5642,28 +5650,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Republic of Djibouti</t>
+          <t>Syrian Arab Republic</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/dj.png</t>
+          <t>https://flagcdn.com/w320/sy.png</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1066809</v>
+        <v>25620000</v>
       </c>
       <c r="F170" t="b">
         <v>1</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -5673,28 +5681,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Nauru</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Republic of Nauru</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/nr.png</t>
+          <t>https://flagcdn.com/w320/ro.png</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>11680</v>
+        <v>19036031</v>
       </c>
       <c r="F171" t="b">
         <v>1</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Southeast Europe</t>
         </is>
       </c>
     </row>
@@ -5704,21 +5712,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Republic of El Salvador</t>
+          <t>Republic of Guatemala</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sv.png</t>
+          <t>https://flagcdn.com/w320/gt.png</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6029976</v>
+        <v>18079810</v>
       </c>
       <c r="F172" t="b">
         <v>1</v>
@@ -5735,28 +5743,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Åland Islands</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Åland Islands</t>
+          <t>Federal Democratic Republic of Nepal</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ax.png</t>
+          <t>https://flagcdn.com/w320/np.png</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>30654</v>
+        <v>29911840</v>
       </c>
       <c r="F173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Southern Asia</t>
         </is>
       </c>
     </row>
@@ -5766,28 +5774,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Guadeloupe</t>
+          <t>Réunion</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Guadeloupe</t>
+          <t>Réunion Island</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gp.png</t>
+          <t>https://flagcdn.com/w320/re.png</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>378561</v>
+        <v>896175</v>
       </c>
       <c r="F174" t="b">
         <v>0</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -5797,28 +5805,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Republic of Honduras</t>
+          <t>Republic of Benin</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/hn.png</t>
+          <t>https://flagcdn.com/w320/bj.png</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>9892632</v>
+        <v>13224860</v>
       </c>
       <c r="F175" t="b">
         <v>1</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -5828,28 +5836,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Republic of Kenya</t>
+          <t>State of Kuwait</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ke.png</t>
+          <t>https://flagcdn.com/w320/kw.png</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>53330978</v>
+        <v>4881254</v>
       </c>
       <c r="F176" t="b">
         <v>1</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -5859,28 +5867,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Republic of Malta</t>
+          <t>Republic of Suriname</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mt.png</t>
+          <t>https://flagcdn.com/w320/sr.png</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>574250</v>
+        <v>616500</v>
       </c>
       <c r="F177" t="b">
         <v>1</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -5890,28 +5898,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>New Caledonia</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Republic of Latvia</t>
+          <t>New Caledonia</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/lv.png</t>
+          <t>https://flagcdn.com/w320/nc.png</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1829000</v>
+        <v>264596</v>
       </c>
       <c r="F178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Melanesia</t>
         </is>
       </c>
     </row>
@@ -5921,28 +5929,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Gabonese Republic</t>
+          <t>Republic of the Sudan</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ga.png</t>
+          <t>https://flagcdn.com/w320/sd.png</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2469296</v>
+        <v>51662000</v>
       </c>
       <c r="F179" t="b">
         <v>1</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>Northern Africa</t>
         </is>
       </c>
     </row>
@@ -5952,28 +5960,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United States Minor Outlying Islands</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hong Kong Special Administrative Region of the People's Republic of China</t>
+          <t>United States Minor Outlying Islands</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/hk.png</t>
+          <t>https://flagcdn.com/w320/um.png</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>7527500</v>
+        <v>0</v>
       </c>
       <c r="F180" t="b">
         <v>0</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -5983,28 +5991,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Svalbard and Jan Mayen</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Svalbard og Jan Mayen</t>
+          <t>Republic of Chad</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sj.png</t>
+          <t>https://flagcdn.com/w320/td.png</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2530</v>
+        <v>19340757</v>
       </c>
       <c r="F181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Middle Africa</t>
         </is>
       </c>
     </row>
@@ -6014,28 +6022,28 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Oriental Republic of Uruguay</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tv.png</t>
+          <t>https://flagcdn.com/w320/uy.png</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>10643</v>
+        <v>3499451</v>
       </c>
       <c r="F182" t="b">
         <v>1</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -6045,28 +6053,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Democratic Republic of Timor-Leste</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tl.png</t>
+          <t>https://flagcdn.com/w320/ba.png</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1391221</v>
+        <v>3422000</v>
       </c>
       <c r="F183" t="b">
         <v>1</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>South-Eastern Asia</t>
+          <t>Southeast Europe</t>
         </is>
       </c>
     </row>
@@ -6076,28 +6084,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Western Sahara</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Sahrawi Arab Democratic Republic</t>
+          <t>Republic of Trinidad and Tobago</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/eh.png</t>
+          <t>https://flagcdn.com/w320/tt.png</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>600904</v>
+        <v>1367764</v>
       </c>
       <c r="F184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -6107,28 +6115,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Kingdom of Lesotho</t>
+          <t>Kingdom of Sweden</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ls.png</t>
+          <t>https://flagcdn.com/w320/se.png</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2116427</v>
+        <v>10605098</v>
       </c>
       <c r="F185" t="b">
         <v>1</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -6138,28 +6146,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/us.png</t>
+          <t>https://flagcdn.com/w320/is.png</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>340110988</v>
+        <v>391810</v>
       </c>
       <c r="F186" t="b">
         <v>1</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -6169,28 +6177,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Kingdom of Thailand</t>
+          <t>Republic of Haiti</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/th.png</t>
+          <t>https://flagcdn.com/w320/ht.png</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>65859640</v>
+        <v>11867032</v>
       </c>
       <c r="F187" t="b">
         <v>1</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>South-Eastern Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -6200,28 +6208,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>British Indian Ocean Territory</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>British Indian Ocean Territory</t>
+          <t>Nation of Brunei, Abode of Peace</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/io.png</t>
+          <t>https://flagcdn.com/w320/bn.png</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>455500</v>
       </c>
       <c r="F188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -6231,30 +6239,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>French Southern and Antarctic Lands</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Republic of India</t>
+          <t>Territory of the French Southern and Antarctic Lands</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/in.png</t>
+          <t>https://flagcdn.com/w320/tf.png</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1417492000</v>
+        <v>400</v>
       </c>
       <c r="F189" t="b">
-        <v>1</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Southern Asia</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6262,24 +6266,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Guernsey</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Republic of Lithuania</t>
+          <t>Bailiwick of Guernsey</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/lt.png</t>
+          <t>https://flagcdn.com/w320/gg.png</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2894886</v>
+        <v>64781</v>
       </c>
       <c r="F190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -6293,28 +6297,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Montserrat</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Montserrat</t>
+          <t>Republic of Croatia</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ms.png</t>
+          <t>https://flagcdn.com/w320/hr.png</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4386</v>
+        <v>3866233</v>
       </c>
       <c r="F191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Southeast Europe</t>
         </is>
       </c>
     </row>
@@ -6324,28 +6328,28 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Saint Barthélemy</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Republic of Zimbabwe</t>
+          <t>Collectivity of Saint Barthélemy</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/zw.png</t>
+          <t>https://flagcdn.com/w320/bl.png</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>17073087</v>
+        <v>10562</v>
       </c>
       <c r="F192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -6355,28 +6359,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Falkland Islands</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Falkland Islands</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/fk.png</t>
+          <t>https://flagcdn.com/w320/mn.png</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>3662</v>
+        <v>3544835</v>
       </c>
       <c r="F193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -6386,28 +6390,28 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Republic of the Maldives</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mv.png</t>
+          <t>https://flagcdn.com/w320/aw.png</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>515132</v>
+        <v>107566</v>
       </c>
       <c r="F194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -6417,28 +6421,28 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Republic of the Congo</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Tunisian Republic</t>
+          <t>Republic of the Congo</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/tn.png</t>
+          <t>https://flagcdn.com/w320/cg.png</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>11972169</v>
+        <v>6142180</v>
       </c>
       <c r="F195" t="b">
         <v>1</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
     </row>
@@ -6448,28 +6452,28 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>São Tomé and Príncipe</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Republic of Estonia</t>
+          <t>Democratic Republic of São Tomé and Príncipe</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ee.png</t>
+          <t>https://flagcdn.com/w320/st.png</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1369995</v>
+        <v>209607</v>
       </c>
       <c r="F196" t="b">
         <v>1</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Middle Africa</t>
         </is>
       </c>
     </row>
@@ -6479,28 +6483,28 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>People's Republic of Bangladesh</t>
+          <t>Republic of Yemen</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bd.png</t>
+          <t>https://flagcdn.com/w320/ye.png</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>169828911</v>
+        <v>32684503</v>
       </c>
       <c r="F197" t="b">
         <v>1</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -6510,28 +6514,28 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Republic of Uzbekistan</t>
+          <t>Republic of Equatorial Guinea</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/uz.png</t>
+          <t>https://flagcdn.com/w320/gq.png</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>37859698</v>
+        <v>1668768</v>
       </c>
       <c r="F198" t="b">
         <v>1</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Middle Africa</t>
         </is>
       </c>
     </row>
@@ -6541,28 +6545,28 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Svalbard and Jan Mayen</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Republic of Ghana</t>
+          <t>Svalbard og Jan Mayen</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/gh.png</t>
+          <t>https://flagcdn.com/w320/sj.png</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>33742380</v>
+        <v>2530</v>
       </c>
       <c r="F199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -6572,28 +6576,28 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Kingdom of Norway</t>
+          <t>Republic of Colombia</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/no.png</t>
+          <t>https://flagcdn.com/w320/co.png</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5606944</v>
+        <v>53057212</v>
       </c>
       <c r="F200" t="b">
         <v>1</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -6603,28 +6607,28 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Federal Republic of Somalia</t>
+          <t>Republic of Guinea-Bissau</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/so.png</t>
+          <t>https://flagcdn.com/w320/gw.png</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>19655000</v>
+        <v>1781308</v>
       </c>
       <c r="F201" t="b">
         <v>1</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -6634,28 +6638,28 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Kiribati</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Commonwealth of the Bahamas</t>
+          <t>Independent and Sovereign Republic of Kiribati</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bs.png</t>
+          <t>https://flagcdn.com/w320/ki.png</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>398165</v>
+        <v>120740</v>
       </c>
       <c r="F202" t="b">
         <v>1</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Micronesia</t>
         </is>
       </c>
     </row>
@@ -6665,28 +6669,28 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Sultanate of Oman</t>
+          <t>Federal Republic of Germany</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/om.png</t>
+          <t>https://flagcdn.com/w320/de.png</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5343630</v>
+        <v>83491249</v>
       </c>
       <c r="F203" t="b">
         <v>1</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Western Europe</t>
         </is>
       </c>
     </row>
@@ -6696,28 +6700,28 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Grand Duchy of Luxembourg</t>
+          <t>Kingdom of Thailand</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/lu.png</t>
+          <t>https://flagcdn.com/w320/th.png</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>681973</v>
+        <v>65859640</v>
       </c>
       <c r="F204" t="b">
         <v>1</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -6727,28 +6731,28 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Isle of Man</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Republic of Iraq</t>
+          <t>Isle of Man</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/iq.png</t>
+          <t>https://flagcdn.com/w320/im.png</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>46118793</v>
+        <v>84530</v>
       </c>
       <c r="F205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -6758,28 +6762,28 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>United States Virgin Islands</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Virgin Islands of the United States</t>
+          <t>Kingdom of Bhutan</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/vi.png</t>
+          <t>https://flagcdn.com/w320/bt.png</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>87146</v>
+        <v>784043</v>
       </c>
       <c r="F206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Southern Asia</t>
         </is>
       </c>
     </row>
@@ -6789,28 +6793,28 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Islamic Republic of Mauritania</t>
+          <t>Gabonese Republic</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mr.png</t>
+          <t>https://flagcdn.com/w320/ga.png</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4927532</v>
+        <v>2469296</v>
       </c>
       <c r="F207" t="b">
         <v>1</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
     </row>
@@ -6820,28 +6824,28 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Sint Maarten</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Sint Maarten</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ca.png</t>
+          <t>https://flagcdn.com/w320/sx.png</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>41651653</v>
+        <v>41349</v>
       </c>
       <c r="F208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -6851,28 +6855,28 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Republic of the Union of Myanmar</t>
+          <t>Democratic Socialist Republic of Sri Lanka</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mm.png</t>
+          <t>https://flagcdn.com/w320/lk.png</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>51316756</v>
+        <v>21763170</v>
       </c>
       <c r="F209" t="b">
         <v>1</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>South-Eastern Asia</t>
+          <t>Southern Asia</t>
         </is>
       </c>
     </row>
@@ -6882,28 +6886,28 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Republic of Albania</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/my.png</t>
+          <t>https://flagcdn.com/w320/al.png</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>34231700</v>
+        <v>2363314</v>
       </c>
       <c r="F210" t="b">
         <v>1</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>South-Eastern Asia</t>
+          <t>Southeast Europe</t>
         </is>
       </c>
     </row>
@@ -6913,24 +6917,24 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Cocos (Keeling) Islands</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Territory of the Cocos (Keeling) Islands</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cc.png</t>
+          <t>https://flagcdn.com/w320/nz.png</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>593</v>
+        <v>5324700</v>
       </c>
       <c r="F211" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -6944,28 +6948,28 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Caribbean Netherlands</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bonaire, Sint Eustatius and Saba</t>
+          <t>People's Democratic Republic of Algeria</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bq.png</t>
+          <t>https://flagcdn.com/w320/dz.png</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>31980</v>
+        <v>47400000</v>
       </c>
       <c r="F212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Northern Africa</t>
         </is>
       </c>
     </row>
@@ -6975,28 +6979,28 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Republic of Uganda</t>
+          <t>Republic of San Marino</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ug.png</t>
+          <t>https://flagcdn.com/w320/sm.png</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>45905417</v>
+        <v>34132</v>
       </c>
       <c r="F213" t="b">
         <v>1</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Southern Europe</t>
         </is>
       </c>
     </row>
@@ -7006,28 +7010,28 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Micronesia</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Islamic Republic of Iran</t>
+          <t>Federated States of Micronesia</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ir.png</t>
+          <t>https://flagcdn.com/w320/fm.png</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>85961000</v>
+        <v>105564</v>
       </c>
       <c r="F214" t="b">
         <v>1</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Micronesia</t>
         </is>
       </c>
     </row>
@@ -7037,28 +7041,28 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Saint Helena, Ascension and Tristan da Cunha</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Country of Curaçao</t>
+          <t>Saint Helena, Ascension and Tristan da Cunha</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cw.png</t>
+          <t>https://flagcdn.com/w320/sh.png</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>156115</v>
+        <v>5651</v>
       </c>
       <c r="F215" t="b">
         <v>0</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
     </row>
@@ -7068,28 +7072,28 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Country of Curaçao</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ro.png</t>
+          <t>https://flagcdn.com/w320/cw.png</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>19036031</v>
+        <v>156115</v>
       </c>
       <c r="F216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Southeast Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -7099,28 +7103,28 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Syrian Arab Republic</t>
+          <t>Republic of El Salvador</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/sy.png</t>
+          <t>https://flagcdn.com/w320/sv.png</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>25620000</v>
+        <v>6029976</v>
       </c>
       <c r="F217" t="b">
         <v>1</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Central America</t>
         </is>
       </c>
     </row>
@@ -7130,28 +7134,28 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>Martinique</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Republic of Fiji</t>
+          <t>Martinique</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/fj.png</t>
+          <t>https://flagcdn.com/w320/mq.png</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>900869</v>
+        <v>349925</v>
       </c>
       <c r="F218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -7161,28 +7165,28 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Nauru</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Republic of Nauru</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/aw.png</t>
+          <t>https://flagcdn.com/w320/nr.png</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>107566</v>
+        <v>11680</v>
       </c>
       <c r="F219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Micronesia</t>
         </is>
       </c>
     </row>
@@ -7192,28 +7196,28 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Kingdom of the Netherlands</t>
+          <t>Vatican City State</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/nl.png</t>
+          <t>https://flagcdn.com/w320/va.png</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>18100436</v>
+        <v>882</v>
       </c>
       <c r="F220" t="b">
         <v>1</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
     </row>
@@ -7223,28 +7227,28 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Republic of Peru</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pe.png</t>
+          <t>https://flagcdn.com/w320/gd.png</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>34350244</v>
+        <v>109021</v>
       </c>
       <c r="F221" t="b">
         <v>1</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -7254,28 +7258,28 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Réunion</t>
+          <t>Tonga</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Réunion Island</t>
+          <t>Kingdom of Tonga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/re.png</t>
+          <t>https://flagcdn.com/w320/to.png</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>896175</v>
+        <v>100179</v>
       </c>
       <c r="F222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Polynesia</t>
         </is>
       </c>
     </row>
@@ -7285,28 +7289,28 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Republic of Botswana</t>
+          <t>Republic of Burundi</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bw.png</t>
+          <t>https://flagcdn.com/w320/bi.png</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2359609</v>
+        <v>12332788</v>
       </c>
       <c r="F223" t="b">
         <v>1</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -7316,28 +7320,28 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Samoa</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Islamic Republic of Afghanistan</t>
+          <t>Independent State of Samoa</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Flag_of_the_Taliban.svg/320px-Flag_of_the_Taliban.svg.png</t>
+          <t>https://flagcdn.com/w320/ws.png</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>43844000</v>
+        <v>205557</v>
       </c>
       <c r="F224" t="b">
         <v>1</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>Polynesia</t>
         </is>
       </c>
     </row>
@@ -7347,28 +7351,28 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Republic of Serbia</t>
+          <t>Kingdom of Denmark</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/rs.png</t>
+          <t>https://flagcdn.com/w320/dk.png</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6567783</v>
+        <v>6011488</v>
       </c>
       <c r="F225" t="b">
         <v>1</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Southeast Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -7378,28 +7382,28 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Bolivarian Republic of Venezuela</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cz.png</t>
+          <t>https://flagcdn.com/w320/ve.png</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>10882341</v>
+        <v>28517000</v>
       </c>
       <c r="F226" t="b">
         <v>1</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Central Europe</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -7409,28 +7413,28 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Commonwealth of Dominica</t>
+          <t>Republic of Austria</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/dm.png</t>
+          <t>https://flagcdn.com/w320/at.png</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>67408</v>
+        <v>9200931</v>
       </c>
       <c r="F227" t="b">
         <v>1</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Central Europe</t>
         </is>
       </c>
     </row>
@@ -7440,21 +7444,21 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Republic of Poland</t>
+          <t>Slovak Republic</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/pl.png</t>
+          <t>https://flagcdn.com/w320/sk.png</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>37392000</v>
+        <v>5413813</v>
       </c>
       <c r="F228" t="b">
         <v>1</v>
@@ -7471,28 +7475,28 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Republic of Benin</t>
+          <t>People's Republic of China</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bj.png</t>
+          <t>https://flagcdn.com/w320/cn.png</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>13224860</v>
+        <v>1408280000</v>
       </c>
       <c r="F229" t="b">
         <v>1</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -7502,28 +7506,28 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>British Indian Ocean Territory</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Republic of Moldova</t>
+          <t>British Indian Ocean Territory</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/md.png</t>
+          <t>https://flagcdn.com/w320/io.png</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2749076</v>
+        <v>0</v>
       </c>
       <c r="F230" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -7533,28 +7537,28 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>French Polynesia</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Russian Federation</t>
+          <t>French Polynesia</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ru.png</t>
+          <t>https://flagcdn.com/w320/pf.png</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>146028325</v>
+        <v>279500</v>
       </c>
       <c r="F231" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Polynesia</t>
         </is>
       </c>
     </row>
@@ -7564,28 +7568,28 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Saint Barthélemy</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Collectivity of Saint Barthélemy</t>
+          <t>Plurinational State of Bolivia</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bl.png</t>
+          <t>https://flagcdn.com/w320/bo.png</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>10562</v>
+        <v>11365333</v>
       </c>
       <c r="F232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -7595,30 +7599,26 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Republic of Indonesia</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/id.png</t>
+          <t>https://flagcdn.com/w320/aq.png</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>284438782</v>
+        <v>1300</v>
       </c>
       <c r="F233" t="b">
-        <v>1</v>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>South-Eastern Asia</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -7626,28 +7626,28 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Republic of Nicaragua</t>
+          <t>State of Libya</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ni.png</t>
+          <t>https://flagcdn.com/w320/ly.png</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6803886</v>
+        <v>7459000</v>
       </c>
       <c r="F234" t="b">
         <v>1</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Northern Africa</t>
         </is>
       </c>
     </row>
@@ -7657,28 +7657,28 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Republic of Armenia</t>
+          <t>Republic of Estonia</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/am.png</t>
+          <t>https://flagcdn.com/w320/ee.png</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>3076200</v>
+        <v>1369995</v>
       </c>
       <c r="F235" t="b">
         <v>1</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -7688,28 +7688,28 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Cook Islands</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Republic of Belarus</t>
+          <t>Cook Islands</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/by.png</t>
+          <t>https://flagcdn.com/w320/ck.png</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>9109280</v>
+        <v>15040</v>
       </c>
       <c r="F236" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Polynesia</t>
         </is>
       </c>
     </row>
@@ -7719,28 +7719,28 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Federal Democratic Republic of Ethiopia</t>
+          <t>Commonwealth of Puerto Rico</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/et.png</t>
+          <t>https://flagcdn.com/w320/pr.png</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>111652998</v>
+        <v>3203295</v>
       </c>
       <c r="F237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -7750,28 +7750,28 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Republic of Costa Rica</t>
+          <t>Republic of Belarus</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cr.png</t>
+          <t>https://flagcdn.com/w320/by.png</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5309625</v>
+        <v>9109280</v>
       </c>
       <c r="F238" t="b">
         <v>1</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
     </row>
@@ -7781,28 +7781,28 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Faroe Islands</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Hashemite Kingdom of Jordan</t>
+          <t>Faroe Islands</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/jo.png</t>
+          <t>https://flagcdn.com/w320/fo.png</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>11734000</v>
+        <v>54885</v>
       </c>
       <c r="F239" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Northern Europe</t>
         </is>
       </c>
     </row>
@@ -7812,28 +7812,28 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Saint Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Federal Republic of Germany</t>
+          <t>Saint Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/de.png</t>
+          <t>https://flagcdn.com/w320/vc.png</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>83491249</v>
+        <v>110872</v>
       </c>
       <c r="F240" t="b">
         <v>1</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -7843,28 +7843,28 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Republic of Ecuador</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ec.png</t>
+          <t>https://flagcdn.com/w320/do.png</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>18103660</v>
+        <v>10771504</v>
       </c>
       <c r="F241" t="b">
         <v>1</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Caribbean</t>
         </is>
       </c>
     </row>
@@ -7874,28 +7874,28 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Democratic People's Republic of Korea</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/kp.png</t>
+          <t>https://flagcdn.com/w320/hu.png</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>25950000</v>
+        <v>9539502</v>
       </c>
       <c r="F242" t="b">
         <v>1</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Central Europe</t>
         </is>
       </c>
     </row>
@@ -7905,28 +7905,28 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Kingdom of Bahrain</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/is.png</t>
+          <t>https://flagcdn.com/w320/bh.png</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>391810</v>
+        <v>1594654</v>
       </c>
       <c r="F243" t="b">
         <v>1</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
@@ -7936,21 +7936,21 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Republic of South Sudan</t>
+          <t>Republic of Cameroon</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ss.png</t>
+          <t>https://flagcdn.com/w320/cm.png</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>15786898</v>
+        <v>29442327</v>
       </c>
       <c r="F244" t="b">
         <v>1</v>
@@ -7967,28 +7967,28 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Republic of Malawi</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/mw.png</t>
+          <t>https://flagcdn.com/w320/ca.png</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>20734262</v>
+        <v>41651653</v>
       </c>
       <c r="F245" t="b">
         <v>1</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Eastern Africa</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -7998,28 +7998,28 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>State of Eritrea</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bf.png</t>
+          <t>https://flagcdn.com/w320/er.png</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>24070553</v>
+        <v>3607000</v>
       </c>
       <c r="F246" t="b">
         <v>1</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Eastern Africa</t>
         </is>
       </c>
     </row>
@@ -8029,28 +8029,28 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Republic of Singapore</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/cd.png</t>
+          <t>https://flagcdn.com/w320/sg.png</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>112832000</v>
+        <v>6110200</v>
       </c>
       <c r="F247" t="b">
         <v>1</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Middle Africa</t>
+          <t>South-Eastern Asia</t>
         </is>
       </c>
     </row>
@@ -8060,28 +8060,28 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Bolivarian Republic of Venezuela</t>
+          <t>Republic of Costa Rica</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/ve.png</t>
+          <t>https://flagcdn.com/w320/cr.png</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>28517000</v>
+        <v>5309625</v>
       </c>
       <c r="F248" t="b">
         <v>1</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Central America</t>
         </is>
       </c>
     </row>
@@ -8091,28 +8091,28 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Nation of Brunei, Abode of Peace</t>
+          <t>Republic of Serbia</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bn.png</t>
+          <t>https://flagcdn.com/w320/rs.png</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>455500</v>
+        <v>6567783</v>
       </c>
       <c r="F249" t="b">
         <v>1</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>South-Eastern Asia</t>
+          <t>Southeast Europe</t>
         </is>
       </c>
     </row>
@@ -8122,28 +8122,28 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Republic of Paraguay</t>
+          <t>Republic of Poland</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/py.png</t>
+          <t>https://flagcdn.com/w320/pl.png</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6109644</v>
+        <v>37392000</v>
       </c>
       <c r="F250" t="b">
         <v>1</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Central Europe</t>
         </is>
       </c>
     </row>
@@ -8153,28 +8153,28 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Republic of Bulgaria</t>
+          <t>Hashemite Kingdom of Jordan</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://flagcdn.com/w320/bg.png</t>
+          <t>https://flagcdn.com/w320/jo.png</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6437360</v>
+        <v>11734000</v>
       </c>
       <c r="F251" t="b">
         <v>1</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Southeast Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
     </row>
